--- a/Data/Home/Balcony.Brightness.xlsx
+++ b/Data/Home/Balcony.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1710405470</v>
+        <v>1712055513</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1710405499</v>
+        <v>1712055530</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1710405523</v>
+        <v>1712055550</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1711631782</v>
+        <v>1712217805</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1711631802</v>
+        <v>1712217823</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1711631820</v>
+        <v>1712217839</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,997 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1712219824</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1712219839</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1712219853</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1712308019</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1712308040</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1712308055</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1712741345</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1712741357</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1712741370</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1712821902</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1712821916</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1712821931</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1712821959</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1712821981</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1712821995</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1712824029</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1712824048</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1712824065</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1713014494</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1713014506</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1713014521</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1713179025</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1713179041</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1713179054</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1713441422</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1713441439</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1713441460</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ExcessivelyBright</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1713441807</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: ComfortableBrightness</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1713441825</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dim</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Brightness_Change</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Balcony</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1713441840</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Balcony.Brightness.state: Dark</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
